--- a/data/trans_orig/P79A7_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A7_2023-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,27 +2440,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
